--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonggun/GH/tdGenS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158F5120-00EA-A548-A4B0-E18E497A2DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5807E1-6140-9E4F-A221-EFC9186D1AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11500" yWindow="9420" windowWidth="27140" windowHeight="16600" xr2:uid="{C0479775-D06F-E545-A426-BB7E1DEBC53E}"/>
+    <workbookView xWindow="8200" yWindow="3580" windowWidth="27140" windowHeight="21480" xr2:uid="{C0479775-D06F-E545-A426-BB7E1DEBC53E}"/>
   </bookViews>
   <sheets>
     <sheet name="A03" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t>SELCTED</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="46">
   <si>
     <t>MaterialCode</t>
   </si>
@@ -69,6 +66,114 @@
   </si>
   <si>
     <t>D511</t>
+  </si>
+  <si>
+    <t>&lt;TransactionRequest&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;Header&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;PlantId&gt;P150&lt;/PlantId&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;SourceSystem&gt;ERP&lt;/SourceSystem&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;DestinationSystem&gt;MES&lt;/DestinationSystem&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;TransactionType&gt;A3&lt;/TransactionType&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;/Header&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;DataS/&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/TransactionRequest&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;TransactionId&gt;359036&lt;/TransactionId&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;Data&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;SourcePlant&gt;D100&lt;/SourcePlant&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;DestinationPlant&gt;P150&lt;/DestinationPlant&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;MaterialCode&gt;1000181&lt;/MaterialCode&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;ControlNo&gt;260321681&lt;/ControlNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;GRFT_Quantity&gt;1000&lt;/GRFT_Quantity&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;QMNo_ofContainers&gt;10&lt;/QMNo_ofContainers&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;Quantity&gt;100.000&lt;/Quantity&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;UOM&gt;kg&lt;/UOM&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;SourceLocation&gt;5111&lt;/SourceLocation&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;TargetLocation&gt;D511&lt;/TargetLocation&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;TransferOrderNo&gt;2817933&lt;/TransferOrderNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;TransferOrderItemNo&gt;1&lt;/TransferOrderItemNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;ExpiryDate&gt;20261231&lt;/ExpiryDate&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;DeletionFlag/&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;/Data&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;ControlNo&gt;20260101999&lt;/ControlNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;TransferOrderItemNo&gt;2&lt;/TransferOrderItemNo&gt;</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;TransactionId&gt;360494&lt;/TransactionId&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;ControlNo&gt;260321890&lt;/ControlNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;Quantity&gt;100&lt;/Quantity&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;TransferOrderNo&gt;8343843&lt;/TransferOrderNo&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      &lt;Quantity&gt;200&lt;/Quantity&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;TransactionId&gt;466123&lt;/TransactionId&gt;</t>
+  </si>
+  <si>
+    <t>SELECTED</t>
   </si>
 </sst>
 </file>
@@ -124,14 +229,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{263BD8B5-C195-854F-8F4C-3027EE477A9F}" name="AThree" displayName="AThree" ref="A1:I12" totalsRowShown="0">
-  <autoFilter ref="A1:I12" xr:uid="{263BD8B5-C195-854F-8F4C-3027EE477A9F}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{FD646D14-4C7E-864A-960D-A4F9DB85F632}" name="SELCTED"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{263BD8B5-C195-854F-8F4C-3027EE477A9F}" name="AThree" displayName="AThree" ref="A1:J3" totalsRowShown="0">
+  <autoFilter ref="A1:J3" xr:uid="{263BD8B5-C195-854F-8F4C-3027EE477A9F}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{FD646D14-4C7E-864A-960D-A4F9DB85F632}" name="SELECTED"/>
     <tableColumn id="2" xr3:uid="{C0D6980E-48DF-7942-B519-2740250E13D2}" name="MaterialCode"/>
     <tableColumn id="3" xr3:uid="{29528942-C3B8-194D-9943-48D8EAFAF61D}" name="ControlNo"/>
     <tableColumn id="4" xr3:uid="{B408D43C-196A-334B-A941-8FB0CB9FCB84}" name="GRFT_Quantity"/>
     <tableColumn id="5" xr3:uid="{43BECA12-5B7A-8D4E-B65E-2C12EA476582}" name="QMNo_ofContainers"/>
+    <tableColumn id="10" xr3:uid="{4AFCA72B-7BB8-0741-A54C-1BADC7C610C4}" name="Quantity"/>
     <tableColumn id="6" xr3:uid="{9DF05D3E-3836-5E40-A3D6-A074E4106184}" name="UOM"/>
     <tableColumn id="7" xr3:uid="{13DF4A42-2635-9E4C-B817-7B0390F9D244}" name="SourceLocation"/>
     <tableColumn id="8" xr3:uid="{CCFF4F7D-971E-0549-8112-D18D30EF4E32}" name="TargetLocation"/>
@@ -458,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8380C1EB-4944-D543-B0FA-AA432D0F20A1}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -471,36 +577,39 @@
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -513,17 +622,20 @@
       <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>5111</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="G2">
-        <v>5111</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -539,14 +651,498 @@
       <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>5111</v>
+      </c>
+      <c r="I3" t="s">
         <v>9</v>
       </c>
-      <c r="G3">
-        <v>5111</v>
-      </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E35" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E43" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" t="s">
+        <v>37</v>
+      </c>
+      <c r="L43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E44" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="L46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonggun/GH/tdGenS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C286790-AA53-4448-A1BA-D087241233B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A373EF-8282-A94A-8F12-24632A2DC302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1960" windowWidth="27140" windowHeight="21480" activeTab="3" xr2:uid="{C0479775-D06F-E545-A426-BB7E1DEBC53E}"/>
+    <workbookView xWindow="9780" yWindow="1820" windowWidth="27140" windowHeight="21480" activeTab="2" xr2:uid="{C0479775-D06F-E545-A426-BB7E1DEBC53E}"/>
   </bookViews>
   <sheets>
     <sheet name="A03" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="A13" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="AFour">ATwo4[]</definedName>
+    <definedName name="AFour">Component[]</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>MaterialCode</t>
   </si>
@@ -98,9 +98,6 @@
     <t>ComponentUOM</t>
   </si>
   <si>
-    <t>TargetStorageLocation</t>
-  </si>
-  <si>
     <t>ValidDecimalPointNo</t>
   </si>
   <si>
@@ -135,6 +132,48 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>ProductionOrderNo</t>
+  </si>
+  <si>
+    <t>ProductionQuantity</t>
+  </si>
+  <si>
+    <t>ProductUOM</t>
+  </si>
+  <si>
+    <t>BatchStartDateTime</t>
+  </si>
+  <si>
+    <t>BatchEndDateTime</t>
+  </si>
+  <si>
+    <t>BOMAlternativeNo</t>
+  </si>
+  <si>
+    <t>ReservationNo</t>
+  </si>
+  <si>
+    <t>OperationNo</t>
+  </si>
+  <si>
+    <t>OperationDescription</t>
+  </si>
+  <si>
+    <t>MBRDocumentNo</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>A5OAM01</t>
+  </si>
+  <si>
+    <t>g</t>
   </si>
 </sst>
 </file>
@@ -201,12 +240,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -245,6 +283,13 @@
       </fill>
     </dxf>
     <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -268,13 +313,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -308,35 +346,58 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{49472F4F-FE82-CD48-B469-5717305D3250}" name="ATwo" displayName="ATwo" ref="A1:D3" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:D3" xr:uid="{49472F4F-FE82-CD48-B469-5717305D3250}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{49472F4F-FE82-CD48-B469-5717305D3250}" name="ATwo" displayName="ATwo" ref="A1:E3" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:E3" xr:uid="{49472F4F-FE82-CD48-B469-5717305D3250}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3A387A65-40DC-DF43-8AF1-24DCF860F087}" name="SELECTED"/>
     <tableColumn id="2" xr3:uid="{349C1C0E-F860-CE49-A059-8976966E4299}" name="MaterialCode"/>
     <tableColumn id="3" xr3:uid="{E61365FA-C712-E545-87B9-CE67BDA925D3}" name="BatchNo"/>
     <tableColumn id="4" xr3:uid="{ADE08523-03D4-F04E-A835-974D4003D724}" name="BatchStatus"/>
+    <tableColumn id="5" xr3:uid="{87F47F41-B59F-F044-9CE3-61AE687C92F6}" name="ExpiryDate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C322A77A-E2A7-D84B-AB08-CEF89DDE689A}" name="ATwo4" displayName="ATwo4" ref="A1:G3" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:G3" xr:uid="{C322A77A-E2A7-D84B-AB08-CEF89DDE689A}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C322A77A-E2A7-D84B-AB08-CEF89DDE689A}" name="Component" displayName="Component" ref="A14:H16" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A14:H16" xr:uid="{C322A77A-E2A7-D84B-AB08-CEF89DDE689A}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{FD78DDD3-322C-2047-BF39-F43E7F716749}" name="SELECTED"/>
     <tableColumn id="2" xr3:uid="{B3008822-0305-9A48-B850-1C91CD8327E0}" name="ReservationItemNo"/>
     <tableColumn id="3" xr3:uid="{5ACB8CDF-4C8E-9C41-B462-971C609E4C4F}" name="ItemNo"/>
     <tableColumn id="4" xr3:uid="{244D9408-CB47-1944-B9A4-C131BA07BDF4}" name="ComponentCode"/>
     <tableColumn id="5" xr3:uid="{920B253C-9E3C-7A49-8FFB-2BF6420C795E}" name="ComponentUOM"/>
-    <tableColumn id="6" xr3:uid="{C4A39D77-09FC-0A42-B6FD-0A8F4677F398}" name="TargetStorageLocation"/>
-    <tableColumn id="7" xr3:uid="{04FC5CC8-9D68-024D-883A-534955DEF292}" name="ValidDecimalPointNo"/>
+    <tableColumn id="6" xr3:uid="{C4A39D77-09FC-0A42-B6FD-0A8F4677F398}" name="Target"/>
+    <tableColumn id="7" xr3:uid="{04FC5CC8-9D68-024D-883A-534955DEF292}" name="StorageLocation"/>
+    <tableColumn id="8" xr3:uid="{ABB299FC-6ADE-BE4C-8FA6-E16286E21BBD}" name="ValidDecimalPointNo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A1087394-40EC-B74C-9CF4-97E6C8341D62}" name="PO" displayName="PO" ref="A1:L4" totalsRowShown="0">
+  <autoFilter ref="A1:L4" xr:uid="{A1087394-40EC-B74C-9CF4-97E6C8341D62}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{36111FF3-7FFD-524E-94F4-6AFB581AEDE8}" name="SELECTED"/>
+    <tableColumn id="2" xr3:uid="{5392A311-A0E9-B94E-A974-881948259E7A}" name="ProductionOrderNo"/>
+    <tableColumn id="3" xr3:uid="{C7D947B9-8D56-034E-9ECF-394AC16FC857}" name="ProductionQuantity"/>
+    <tableColumn id="4" xr3:uid="{77DAEC42-246D-954C-B0FD-440570D16CAE}" name="ProductUOM"/>
+    <tableColumn id="5" xr3:uid="{DECA5100-0E43-404C-9F94-80A051250BD5}" name="BatchNo"/>
+    <tableColumn id="6" xr3:uid="{5E2E36C1-2999-F043-B198-C58681F26ABC}" name="BatchStartDateTime"/>
+    <tableColumn id="7" xr3:uid="{7C1FBB2E-3917-EA41-A3C2-71B21DF000E2}" name="BatchEndDateTime"/>
+    <tableColumn id="8" xr3:uid="{1A3495AE-C0E6-394F-81F7-3CD9FFC02B55}" name="BOMAlternativeNo"/>
+    <tableColumn id="9" xr3:uid="{CDE46CC8-E62B-F140-AA6A-F7A390DF1B6D}" name="ReservationNo"/>
+    <tableColumn id="10" xr3:uid="{1A1BC38C-C152-8249-BB53-15986B93ABAB}" name="OperationNo"/>
+    <tableColumn id="11" xr3:uid="{8009FAD5-8B24-A34F-96A1-609BD71C3B6B}" name="OperationDescription"/>
+    <tableColumn id="12" xr3:uid="{FC14FFAA-63CA-704F-BF27-5403E1E0AA69}" name="MBRDocumentNo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CC1CBB0E-82CF-E647-8000-2304108E741E}" name="AThirteen" displayName="AThirteen" ref="A1:L2" totalsRowShown="0">
   <autoFilter ref="A1:L2" xr:uid="{CC1CBB0E-82CF-E647-8000-2304108E741E}"/>
   <tableColumns count="12">
@@ -784,16 +845,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805F6F00-B87A-EE4E-AEC9-38E7763214C1}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -806,8 +868,11 @@
       <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -818,10 +883,13 @@
         <v>260101888</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="E2">
+        <v>20261231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -832,7 +900,10 @@
         <v>260101777</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>20261231</v>
       </c>
     </row>
   </sheetData>
@@ -845,59 +916,152 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E47E6F-8426-4647-B869-3E0AD0D5A035}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B15" s="2">
         <v>1000181</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="C15" s="2"/>
+      <c r="D15">
         <v>1000181</v>
       </c>
-      <c r="C3" s="3">
-        <v>20260101999</v>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1000181</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16">
+        <v>1000181</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -922,10 +1086,10 @@
         <v>11</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -934,25 +1098,25 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
-      </c>
-      <c r="H1" t="s">
-        <v>26</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
       </c>
       <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
-      </c>
-      <c r="L1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -990,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J10" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J12" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:J4"/>
   <tableColumns count="10">
     <tableColumn id="1" name="SELECTED"/>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -877,7 +877,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -902,24 +902,74 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>1000181</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>D511</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="540" yWindow="5100" windowWidth="27140" windowHeight="21480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5520" yWindow="3960" windowWidth="27140" windowHeight="21480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="A03" sheetId="1" state="visible" r:id="rId1"/>
@@ -224,13 +224,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J12" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J8" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:J4"/>
   <tableColumns count="10">
     <tableColumn id="1" name="SELECTED"/>
     <tableColumn id="2" name="MaterialCode"/>
     <tableColumn id="3" name="ControlNo"/>
-    <tableColumn id="4" name="GRFT_Quantity"/>
+    <tableColumn id="4" name="GRTF_Quantity"/>
     <tableColumn id="5" name="QMNo_ofContainers"/>
     <tableColumn id="6" name="Quantity"/>
     <tableColumn id="7" name="UOM"/>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>GRFT_Quantity</t>
+          <t>GRTF_Quantity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -827,7 +827,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -870,106 +870,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1000181</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1000181</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1000181</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1000181</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>D511</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5520" yWindow="3960" windowWidth="27140" windowHeight="21480" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1050" yWindow="1035" windowWidth="26310" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="A03" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,20 +21,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="0"/>
       <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -89,7 +96,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -224,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J10" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:J8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J88" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:J68"/>
   <tableColumns count="10">
     <tableColumn id="1" name="SELECTED"/>
     <tableColumn id="2" name="MaterialCode"/>
@@ -243,7 +250,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATwo" displayName="ATwo" ref="A1:E4" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATwo" displayName="ATwo" ref="A1:E4" headerRowCount="1" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:E4"/>
   <tableColumns count="5">
     <tableColumn id="1" name="SELECTED"/>
@@ -257,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Component" displayName="Component" ref="A14:H16" headerRowCount="1" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A14:H16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Component" displayName="Component" ref="A11:H13" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A11:H13"/>
   <tableColumns count="8">
     <tableColumn id="1" name="SELECTED"/>
     <tableColumn id="2" name="ReservationItemNo"/>
@@ -274,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PO" displayName="PO" ref="A1:L4" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:L4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PO" displayName="PO" ref="A1:L2" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:L2"/>
   <tableColumns count="12">
     <tableColumn id="1" name="SELECTED"/>
     <tableColumn id="2" name="ProductionOrderNo"/>
@@ -636,16 +643,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:J88"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="18.5" customWidth="1" min="2" max="2"/>
+    <col width="18.44140625" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15.6640625" customWidth="1" min="4" max="4"/>
     <col width="20.33203125" customWidth="1" min="5" max="5"/>
     <col width="16.33203125" customWidth="1" min="7" max="8"/>
-    <col width="15.83203125" customWidth="1" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" min="9" max="9"/>
     <col width="12.33203125" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -877,7 +884,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -902,24 +909,2174 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2603296081</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>0</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>0</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>0</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>0</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>0</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2603291255</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
         <v>1</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1000181</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2603296168</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>D511</t>
         </is>
@@ -927,6 +3084,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="150" verticalDpi="150"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -940,11 +3098,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14.6640625" customWidth="1" min="2" max="2"/>
-    <col width="22.5" customWidth="1" min="3" max="3"/>
+    <col width="22.44140625" customWidth="1" min="3" max="3"/>
     <col width="13.6640625" customWidth="1" min="4" max="4"/>
     <col width="18.6640625" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1035,15 +3193,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="19.5" customWidth="1" min="2" max="3"/>
+    <col width="19.44140625" customWidth="1" min="2" max="3"/>
     <col width="18" customWidth="1" min="4" max="5"/>
     <col width="20.33203125" customWidth="1" min="6" max="6"/>
     <col width="19.33203125" customWidth="1" min="7" max="7"/>
-    <col width="18.83203125" customWidth="1" min="8" max="8"/>
+    <col width="18.77734375" customWidth="1" min="8" max="8"/>
     <col width="15.6640625" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="21.33203125" customWidth="1" min="11" max="11"/>
@@ -1130,101 +3288,101 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>SELECTED</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>ReservationItemNo</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>ItemNo</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>ComponentCode</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>ComponentUOM</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>StorageLocation</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>ValidDecimalPointNo</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="12">
+      <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="n">
         <v>1000181</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" t="n">
-        <v>1000181</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>100</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1000181</v>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" t="n">
-        <v>1000181</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" t="n">
+        <v>1000121</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>200</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>D511</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1244,16 +3402,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17.1640625" customWidth="1" min="2" max="2"/>
-    <col width="13.1640625" customWidth="1" min="7" max="7"/>
+    <col width="17.109375" customWidth="1" min="2" max="2"/>
+    <col width="13.109375" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="17.33203125" customWidth="1" min="10" max="10"/>
     <col width="16.6640625" customWidth="1" min="11" max="11"/>
-    <col width="25.1640625" customWidth="1" min="12" max="12"/>
+    <col width="25.109375" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data.xlsx
+++ b/data.xlsx
@@ -231,7 +231,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J88" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AThree" displayName="AThree" ref="A1:J108" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:J68"/>
   <tableColumns count="10">
     <tableColumn id="1" name="SELECTED"/>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3054,29 +3054,629 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2603298707</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>1</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1000181</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2603295474</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>1000121</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2603298707</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>D511</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1000121</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2603299855</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>D511</t>
         </is>
